--- a/www/EQuiPD_260306.xlsx
+++ b/www/EQuiPD_260306.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmork/Documents/GitHub/C40_EQuiPD/www/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DE08D6-D6D5-C242-A6EE-25F8E8944711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94392766-3A3D-FA49-AFD0-05C19776427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="500" windowWidth="30240" windowHeight="17880" xr2:uid="{30BB5428-C633-D247-A3EC-BE7DB74FA751}"/>
   </bookViews>
@@ -3004,6 +3004,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3027,21 +3039,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3089,6 +3086,12 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3127,9 +3130,6 @@
     </xf>
     <xf numFmtId="1" fontId="14" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5481,24 +5481,24 @@
     </row>
     <row r="3" spans="1:9" ht="98" customHeight="1" thickBot="1">
       <c r="B3" s="39"/>
-      <c r="C3" s="182" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="184"/>
+      <c r="C3" s="186" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="188"/>
       <c r="H3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="19">
       <c r="B4" s="39"/>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="185" t="s">
         <v>375</v>
       </c>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="181"/>
-      <c r="G4" s="181"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
       <c r="H4" s="42"/>
     </row>
     <row r="5" spans="1:9" ht="17" customHeight="1">
@@ -5512,20 +5512,20 @@
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1">
       <c r="B6" s="39"/>
-      <c r="C6" s="180" t="s">
+      <c r="C6" s="184" t="s">
         <v>376</v>
       </c>
-      <c r="D6" s="180"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="180"/>
-      <c r="G6" s="180"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
       <c r="H6" s="42"/>
     </row>
     <row r="7" spans="1:9" ht="17" customHeight="1">
       <c r="B7" s="63"/>
-      <c r="C7" s="179"/>
-      <c r="D7" s="179"/>
-      <c r="E7" s="179"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="183"/>
       <c r="F7" s="145"/>
       <c r="G7" s="145"/>
       <c r="H7" s="66"/>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D11" s="99"/>
       <c r="F11" s="177"/>
-      <c r="G11" s="221" t="s">
+      <c r="G11" s="179" t="s">
         <v>509</v>
       </c>
       <c r="H11" s="42"/>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="D20" s="173"/>
       <c r="F20" s="177"/>
-      <c r="G20" s="185" t="s">
+      <c r="G20" s="189" t="s">
         <v>524</v>
       </c>
       <c r="H20" s="42"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D21" s="173"/>
       <c r="F21" s="177"/>
-      <c r="G21" s="186"/>
+      <c r="G21" s="190"/>
       <c r="H21" s="42"/>
     </row>
     <row r="22" spans="2:8" ht="17" thickBot="1">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="D39" s="173"/>
       <c r="F39" s="177"/>
-      <c r="G39" s="187" t="s">
+      <c r="G39" s="180" t="s">
         <v>384</v>
       </c>
       <c r="H39" s="42"/>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D40" s="173"/>
       <c r="F40" s="177"/>
-      <c r="G40" s="188"/>
+      <c r="G40" s="181"/>
       <c r="H40" s="42"/>
     </row>
     <row r="41" spans="1:9" ht="32" customHeight="1" thickBot="1">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D41" s="173"/>
       <c r="F41" s="177"/>
-      <c r="G41" s="189"/>
+      <c r="G41" s="182"/>
       <c r="H41" s="42"/>
     </row>
     <row r="42" spans="1:9">
@@ -5908,6 +5908,7 @@
       <c r="I43" s="4"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="6">
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="C7:E7"/>
@@ -6040,11 +6041,11 @@
     </row>
     <row r="3" spans="1:20" ht="101" customHeight="1" thickBot="1">
       <c r="B3" s="39"/>
-      <c r="C3" s="182" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="183"/>
-      <c r="E3" s="184"/>
+      <c r="C3" s="186" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="187"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="42"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -6062,11 +6063,11 @@
     </row>
     <row r="4" spans="1:20" ht="19">
       <c r="B4" s="39"/>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="185" t="s">
         <v>387</v>
       </c>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
       <c r="F4" s="42"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -6126,11 +6127,11 @@
     </row>
     <row r="7" spans="1:20" ht="115" customHeight="1">
       <c r="B7" s="39"/>
-      <c r="C7" s="199" t="s">
+      <c r="C7" s="198" t="s">
         <v>498</v>
       </c>
-      <c r="D7" s="200"/>
-      <c r="E7" s="201"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="200"/>
       <c r="F7" s="42"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -6148,11 +6149,11 @@
     </row>
     <row r="8" spans="1:20" ht="24" customHeight="1">
       <c r="B8" s="39"/>
-      <c r="C8" s="202" t="s">
+      <c r="C8" s="201" t="s">
         <v>497</v>
       </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="204"/>
+      <c r="D8" s="202"/>
+      <c r="E8" s="203"/>
       <c r="F8" s="42"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
@@ -6170,11 +6171,11 @@
     </row>
     <row r="9" spans="1:20" ht="21" customHeight="1">
       <c r="B9" s="39"/>
-      <c r="C9" s="193" t="s">
+      <c r="C9" s="192" t="s">
         <v>418</v>
       </c>
-      <c r="D9" s="194"/>
-      <c r="E9" s="195"/>
+      <c r="D9" s="193"/>
+      <c r="E9" s="194"/>
       <c r="F9" s="42"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
@@ -6192,11 +6193,11 @@
     </row>
     <row r="10" spans="1:20" ht="34" customHeight="1">
       <c r="B10" s="39"/>
-      <c r="C10" s="193" t="s">
+      <c r="C10" s="192" t="s">
         <v>419</v>
       </c>
-      <c r="D10" s="194"/>
-      <c r="E10" s="195"/>
+      <c r="D10" s="193"/>
+      <c r="E10" s="194"/>
       <c r="F10" s="42"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -6214,11 +6215,11 @@
     </row>
     <row r="11" spans="1:20" ht="34" customHeight="1">
       <c r="B11" s="39"/>
-      <c r="C11" s="193" t="s">
+      <c r="C11" s="192" t="s">
         <v>420</v>
       </c>
-      <c r="D11" s="194"/>
-      <c r="E11" s="195"/>
+      <c r="D11" s="193"/>
+      <c r="E11" s="194"/>
       <c r="F11" s="42"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -6236,11 +6237,11 @@
     </row>
     <row r="12" spans="1:20" ht="34" customHeight="1">
       <c r="B12" s="39"/>
-      <c r="C12" s="193" t="s">
+      <c r="C12" s="192" t="s">
         <v>421</v>
       </c>
-      <c r="D12" s="194"/>
-      <c r="E12" s="195"/>
+      <c r="D12" s="193"/>
+      <c r="E12" s="194"/>
       <c r="F12" s="42"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
@@ -6258,11 +6259,11 @@
     </row>
     <row r="13" spans="1:20" ht="41" customHeight="1" thickBot="1">
       <c r="B13" s="39"/>
-      <c r="C13" s="205" t="s">
+      <c r="C13" s="204" t="s">
         <v>302</v>
       </c>
-      <c r="D13" s="206"/>
-      <c r="E13" s="207"/>
+      <c r="D13" s="205"/>
+      <c r="E13" s="206"/>
       <c r="F13" s="42"/>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
@@ -6280,11 +6281,11 @@
     </row>
     <row r="14" spans="1:20" ht="73" customHeight="1" thickBot="1">
       <c r="B14" s="39"/>
-      <c r="C14" s="196" t="s">
+      <c r="C14" s="195" t="s">
         <v>496</v>
       </c>
-      <c r="D14" s="197"/>
-      <c r="E14" s="198"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="197"/>
       <c r="F14" s="42"/>
       <c r="H14" s="11"/>
       <c r="I14" s="12"/>
@@ -6302,10 +6303,10 @@
     </row>
     <row r="15" spans="1:20">
       <c r="B15" s="39"/>
-      <c r="C15" s="192" t="s">
+      <c r="C15" s="191" t="s">
         <v>373</v>
       </c>
-      <c r="D15" s="192"/>
+      <c r="D15" s="191"/>
       <c r="E15" s="122"/>
       <c r="F15" s="42"/>
       <c r="H15" s="11"/>
@@ -6324,10 +6325,10 @@
     </row>
     <row r="16" spans="1:20">
       <c r="B16" s="39"/>
-      <c r="C16" s="192" t="s">
+      <c r="C16" s="191" t="s">
         <v>492</v>
       </c>
-      <c r="D16" s="192"/>
+      <c r="D16" s="191"/>
       <c r="E16" s="121"/>
       <c r="F16" s="42"/>
       <c r="H16" s="11"/>
@@ -6968,11 +6969,11 @@
         <f>B40</f>
         <v>14</v>
       </c>
-      <c r="C41" s="190" t="s">
+      <c r="C41" s="207" t="s">
         <v>388</v>
       </c>
-      <c r="D41" s="190"/>
-      <c r="E41" s="190"/>
+      <c r="D41" s="207"/>
+      <c r="E41" s="207"/>
       <c r="F41" s="42"/>
     </row>
     <row r="42" spans="2:20" ht="112" hidden="1" outlineLevel="2">
@@ -7510,11 +7511,11 @@
         <f>B62</f>
         <v>33</v>
       </c>
-      <c r="C63" s="190" t="s">
+      <c r="C63" s="207" t="s">
         <v>388</v>
       </c>
-      <c r="D63" s="190"/>
-      <c r="E63" s="190"/>
+      <c r="D63" s="207"/>
+      <c r="E63" s="207"/>
       <c r="F63" s="42"/>
     </row>
     <row r="64" spans="2:20" ht="80" hidden="1" outlineLevel="1">
@@ -7926,11 +7927,11 @@
         <f>B79</f>
         <v>47</v>
       </c>
-      <c r="C80" s="190" t="s">
+      <c r="C80" s="207" t="s">
         <v>388</v>
       </c>
-      <c r="D80" s="190"/>
-      <c r="E80" s="190"/>
+      <c r="D80" s="207"/>
+      <c r="E80" s="207"/>
       <c r="F80" s="42"/>
     </row>
     <row r="81" spans="2:20" ht="48" hidden="1" outlineLevel="1">
@@ -8318,11 +8319,11 @@
         <f>B95</f>
         <v>60</v>
       </c>
-      <c r="C96" s="190" t="s">
+      <c r="C96" s="207" t="s">
         <v>388</v>
       </c>
-      <c r="D96" s="190"/>
-      <c r="E96" s="190"/>
+      <c r="D96" s="207"/>
+      <c r="E96" s="207"/>
       <c r="F96" s="42"/>
     </row>
     <row r="97" spans="2:20" ht="96" hidden="1" outlineLevel="1">
@@ -8743,11 +8744,11 @@
         <f>B112</f>
         <v>74</v>
       </c>
-      <c r="C113" s="190" t="s">
+      <c r="C113" s="207" t="s">
         <v>388</v>
       </c>
-      <c r="D113" s="190"/>
-      <c r="E113" s="190"/>
+      <c r="D113" s="207"/>
+      <c r="E113" s="207"/>
       <c r="F113" s="42"/>
     </row>
     <row r="114" spans="1:20" ht="96" hidden="1" outlineLevel="1">
@@ -8878,17 +8879,17 @@
     </row>
     <row r="120" spans="1:20" ht="27" customHeight="1" collapsed="1">
       <c r="B120" s="39"/>
-      <c r="C120" s="208" t="s">
+      <c r="C120" s="209" t="s">
         <v>499</v>
       </c>
-      <c r="D120" s="208"/>
-      <c r="E120" s="208"/>
+      <c r="D120" s="209"/>
+      <c r="E120" s="209"/>
       <c r="F120" s="42"/>
     </row>
     <row r="121" spans="1:20">
       <c r="B121" s="63"/>
-      <c r="C121" s="191"/>
-      <c r="D121" s="191"/>
+      <c r="C121" s="208"/>
+      <c r="D121" s="208"/>
       <c r="E121" s="157"/>
       <c r="F121" s="66"/>
     </row>
@@ -8927,6 +8928,13 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="19">
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C120:E120"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C3:E3"/>
@@ -8939,13 +8947,6 @@
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="C120:E120"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{F5AED12B-0397-E94D-BEE6-2BC9B21F74F7}">
@@ -9071,11 +9072,11 @@
     <row r="3" spans="1:19" s="5" customFormat="1" ht="73" customHeight="1" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="39"/>
-      <c r="C3" s="182" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="183"/>
-      <c r="E3" s="184"/>
+      <c r="C3" s="186" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="187"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="116"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
@@ -9094,11 +9095,11 @@
     <row r="4" spans="1:19" s="5" customFormat="1" ht="19">
       <c r="A4" s="4"/>
       <c r="B4" s="63"/>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="212" t="s">
         <v>278</v>
       </c>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
       <c r="F4" s="117"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
@@ -9141,10 +9142,10 @@
         <f>"EQuiPD Self-Assessment Scores: "&amp;IF('Self-Assessment'!$D$20="Not listed",'Self-Assessment'!$D$21,'Self-Assessment'!$D$20)&amp;" "&amp;'Self-Assessment'!D$23</f>
         <v xml:space="preserve">EQuiPD Self-Assessment Scores:  </v>
       </c>
-      <c r="E7" s="209" t="s">
+      <c r="E7" s="210" t="s">
         <v>275</v>
       </c>
-      <c r="F7" s="209"/>
+      <c r="F7" s="210"/>
       <c r="G7" s="16" t="s">
         <v>0</v>
       </c>
@@ -9159,30 +9160,30 @@
       <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:19" ht="96" customHeight="1">
-      <c r="B9" s="200" t="s">
+      <c r="B9" s="199" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="200"/>
-      <c r="D9" s="200"/>
-      <c r="E9" s="200"/>
-      <c r="F9" s="200"/>
+      <c r="C9" s="199"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
     </row>
     <row r="10" spans="1:19" ht="16" customHeight="1">
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="210" t="s">
+      <c r="D10" s="211" t="s">
         <v>276</v>
       </c>
-      <c r="E10" s="210"/>
-      <c r="F10" s="210"/>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
     </row>
     <row r="11" spans="1:19">
       <c r="B11" s="21"/>
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="212"/>
-      <c r="E11" s="212"/>
+      <c r="D11" s="213"/>
+      <c r="E11" s="213"/>
       <c r="F11" s="22"/>
     </row>
     <row r="12" spans="1:19" ht="32">
@@ -9324,13 +9325,13 @@
       <c r="F19" s="20"/>
     </row>
     <row r="20" spans="2:6" ht="127" customHeight="1">
-      <c r="B20" s="200" t="s">
+      <c r="B20" s="199" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="200"/>
-      <c r="D20" s="200"/>
-      <c r="E20" s="200"/>
-      <c r="F20" s="200"/>
+      <c r="C20" s="199"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="199"/>
+      <c r="F20" s="199"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="20"/>
@@ -9341,11 +9342,11 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="21"/>
-      <c r="C22" s="212" t="s">
+      <c r="C22" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="212"/>
-      <c r="E22" s="212"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="213"/>
       <c r="F22" s="22"/>
     </row>
     <row r="23" spans="2:6" ht="32">
@@ -9497,13 +9498,13 @@
       <c r="F31" s="20"/>
     </row>
     <row r="32" spans="2:6" ht="155" customHeight="1">
-      <c r="B32" s="200" t="s">
+      <c r="B32" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="200"/>
-      <c r="D32" s="200"/>
-      <c r="E32" s="200"/>
-      <c r="F32" s="200"/>
+      <c r="C32" s="199"/>
+      <c r="D32" s="199"/>
+      <c r="E32" s="199"/>
+      <c r="F32" s="199"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="20"/>
@@ -9514,11 +9515,11 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="21"/>
-      <c r="C34" s="212" t="s">
+      <c r="C34" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="212"/>
-      <c r="E34" s="212"/>
+      <c r="D34" s="213"/>
+      <c r="E34" s="213"/>
       <c r="F34" s="22"/>
     </row>
     <row r="35" spans="2:6" ht="32">
@@ -9660,13 +9661,13 @@
       <c r="F42" s="20"/>
     </row>
     <row r="43" spans="2:6" ht="156" customHeight="1">
-      <c r="B43" s="200" t="s">
+      <c r="B43" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="200"/>
-      <c r="D43" s="200"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
+      <c r="C43" s="199"/>
+      <c r="D43" s="199"/>
+      <c r="E43" s="199"/>
+      <c r="F43" s="199"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="20"/>
@@ -9677,11 +9678,11 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="21"/>
-      <c r="C45" s="212" t="s">
+      <c r="C45" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="212"/>
-      <c r="E45" s="212"/>
+      <c r="D45" s="213"/>
+      <c r="E45" s="213"/>
       <c r="F45" s="22"/>
     </row>
     <row r="46" spans="2:6" ht="32">
@@ -9833,13 +9834,13 @@
       <c r="F54" s="20"/>
     </row>
     <row r="55" spans="2:6" ht="156" customHeight="1">
-      <c r="B55" s="200" t="s">
+      <c r="B55" s="199" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="200"/>
-      <c r="D55" s="200"/>
-      <c r="E55" s="200"/>
-      <c r="F55" s="200"/>
+      <c r="C55" s="199"/>
+      <c r="D55" s="199"/>
+      <c r="E55" s="199"/>
+      <c r="F55" s="199"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="20"/>
@@ -9850,11 +9851,11 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="21"/>
-      <c r="C57" s="212" t="s">
+      <c r="C57" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="D57" s="212"/>
-      <c r="E57" s="212"/>
+      <c r="D57" s="213"/>
+      <c r="E57" s="213"/>
       <c r="F57" s="22"/>
     </row>
     <row r="58" spans="2:6" ht="32">
@@ -9996,13 +9997,13 @@
       <c r="F65" s="20"/>
     </row>
     <row r="66" spans="2:6" ht="152" customHeight="1">
-      <c r="B66" s="200" t="s">
+      <c r="B66" s="199" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="200"/>
-      <c r="D66" s="200"/>
-      <c r="E66" s="200"/>
-      <c r="F66" s="200"/>
+      <c r="C66" s="199"/>
+      <c r="D66" s="199"/>
+      <c r="E66" s="199"/>
+      <c r="F66" s="199"/>
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="20"/>
@@ -10013,11 +10014,11 @@
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="21"/>
-      <c r="C68" s="212" t="s">
+      <c r="C68" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
+      <c r="D68" s="213"/>
+      <c r="E68" s="213"/>
       <c r="F68" s="22"/>
     </row>
     <row r="69" spans="2:6" ht="32">
@@ -10436,11 +10437,11 @@
     </row>
     <row r="3" spans="1:21" ht="73" customHeight="1" thickBot="1">
       <c r="B3" s="39"/>
-      <c r="C3" s="182" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="183"/>
-      <c r="E3" s="184"/>
+      <c r="C3" s="186" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="187"/>
+      <c r="E3" s="188"/>
       <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="I3" s="11"/>
@@ -10459,11 +10460,11 @@
     </row>
     <row r="4" spans="1:21" ht="19" hidden="1">
       <c r="B4" s="39"/>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="185" t="s">
         <v>266</v>
       </c>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
       <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="I4" s="11"/>
@@ -10482,11 +10483,11 @@
     </row>
     <row r="5" spans="1:21" ht="19">
       <c r="B5" s="39"/>
-      <c r="C5" s="181" t="s">
+      <c r="C5" s="185" t="s">
         <v>266</v>
       </c>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
       <c r="F5" s="51"/>
       <c r="G5" s="42"/>
       <c r="I5" s="11"/>
@@ -10505,32 +10506,32 @@
     </row>
     <row r="6" spans="1:21" ht="78" customHeight="1">
       <c r="B6" s="39"/>
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="217" t="s">
         <v>370</v>
       </c>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
       <c r="F6" s="51"/>
       <c r="G6" s="42"/>
-      <c r="I6" s="213" t="s">
+      <c r="I6" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="214"/>
-      <c r="K6" s="214"/>
-      <c r="L6" s="214"/>
-      <c r="M6" s="214"/>
-      <c r="N6" s="215"/>
-      <c r="O6" s="213" t="s">
+      <c r="J6" s="215"/>
+      <c r="K6" s="215"/>
+      <c r="L6" s="215"/>
+      <c r="M6" s="215"/>
+      <c r="N6" s="216"/>
+      <c r="O6" s="214" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="214"/>
-      <c r="Q6" s="214"/>
-      <c r="R6" s="215"/>
-      <c r="S6" s="213" t="s">
+      <c r="P6" s="215"/>
+      <c r="Q6" s="215"/>
+      <c r="R6" s="216"/>
+      <c r="S6" s="214" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="214"/>
-      <c r="U6" s="215"/>
+      <c r="T6" s="215"/>
+      <c r="U6" s="216"/>
     </row>
     <row r="7" spans="1:21" ht="291" customHeight="1">
       <c r="B7" s="101">
@@ -13425,10 +13426,10 @@
       </c>
       <c r="D3" s="42"/>
       <c r="F3" s="39"/>
-      <c r="G3" s="217" t="s">
+      <c r="G3" s="218" t="s">
         <v>487</v>
       </c>
-      <c r="H3" s="218"/>
+      <c r="H3" s="219"/>
       <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="19">
@@ -15580,12 +15581,12 @@
     </row>
     <row r="2" spans="1:10" s="71" customFormat="1" ht="55" customHeight="1">
       <c r="A2" s="70"/>
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="220" t="s">
         <v>235</v>
       </c>
-      <c r="C2" s="219"/>
-      <c r="D2" s="219"/>
-      <c r="E2" s="219"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
       <c r="F2" s="70"/>
     </row>
     <row r="3" spans="1:10" s="71" customFormat="1">
@@ -15608,11 +15609,11 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="76"/>
-      <c r="C6" s="220" t="s">
+      <c r="C6" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="221"/>
     </row>
     <row r="7" spans="1:10" ht="32">
       <c r="B7" s="77" t="s">
@@ -15718,11 +15719,11 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="76"/>
-      <c r="C15" s="220" t="s">
+      <c r="C15" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="220"/>
-      <c r="E15" s="220"/>
+      <c r="D15" s="221"/>
+      <c r="E15" s="221"/>
     </row>
     <row r="16" spans="1:10" s="72" customFormat="1" ht="32">
       <c r="B16" s="77" t="s">
@@ -15860,11 +15861,11 @@
     </row>
     <row r="24" spans="2:10" s="72" customFormat="1">
       <c r="B24" s="76"/>
-      <c r="C24" s="220" t="s">
+      <c r="C24" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="220"/>
-      <c r="E24" s="220"/>
+      <c r="D24" s="221"/>
+      <c r="E24" s="221"/>
       <c r="G24" s="75"/>
       <c r="H24" s="75"/>
       <c r="I24" s="75"/>
@@ -16006,11 +16007,11 @@
     </row>
     <row r="33" spans="2:10" s="72" customFormat="1">
       <c r="B33" s="76"/>
-      <c r="C33" s="220" t="s">
+      <c r="C33" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="220"/>
-      <c r="E33" s="220"/>
+      <c r="D33" s="221"/>
+      <c r="E33" s="221"/>
       <c r="G33" s="75"/>
       <c r="H33" s="75"/>
       <c r="I33" s="75"/>
@@ -16162,11 +16163,11 @@
     </row>
     <row r="43" spans="2:10" s="72" customFormat="1">
       <c r="B43" s="76"/>
-      <c r="C43" s="220" t="s">
+      <c r="C43" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="220"/>
-      <c r="E43" s="220"/>
+      <c r="D43" s="221"/>
+      <c r="E43" s="221"/>
       <c r="G43" s="75"/>
       <c r="H43" s="75"/>
       <c r="I43" s="75"/>
@@ -16308,11 +16309,11 @@
     </row>
     <row r="52" spans="2:10" s="72" customFormat="1">
       <c r="B52" s="76"/>
-      <c r="C52" s="220" t="s">
+      <c r="C52" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="D52" s="220"/>
-      <c r="E52" s="220"/>
+      <c r="D52" s="221"/>
+      <c r="E52" s="221"/>
       <c r="G52" s="75"/>
       <c r="H52" s="75"/>
       <c r="I52" s="75"/>
